--- a/src/make_cv/files/Service/professional development data.xlsx
+++ b/src/make_cv/files/Service/professional development data.xlsx
@@ -1,44 +1,124 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bhelenbr/Codes/make_cv/src/make_cv/files/Service/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D31263-19AC-EB4C-AE3F-CBE80090A4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11700" yWindow="2620" windowWidth="26700" windowHeight="17260" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="3540" yWindow="760" windowWidth="26700" windowHeight="17260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Notes" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$F$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data!$A$1:$F$79</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+  <si>
+    <t>Some Notes</t>
+  </si>
+  <si>
+    <t>Types</t>
+  </si>
+  <si>
+    <t>Teaching</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>Professional</t>
+  </si>
+  <si>
+    <t>Terms</t>
+  </si>
+  <si>
+    <t>Fall</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>Summer</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>Calendar Year</t>
+  </si>
+  <si>
+    <t>Hours</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>name/description of activity</t>
+  </si>
+  <si>
+    <t>not used</t>
+  </si>
+  <si>
+    <t>KEEN Teaching Large Classes</t>
+  </si>
+  <si>
+    <t>This was really useful</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Make an entry for every activity by year. This is not used except for ABET cv's and activity reporting</t>
+  </si>
+  <si>
+    <t>total number of hours for that activity during the semester  (used for activity reporting)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -57,81 +137,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -431,89 +452,135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Some Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Make an entry for every activity by year</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Types</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Teaching</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Professional</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fall</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Spring</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Summer</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Winter</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>2020</v>
+      </c>
+      <c r="E21">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -522,75 +589,66 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F66"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="36.33203125" customWidth="1" min="1" max="1"/>
-    <col width="14.33203125" customWidth="1" min="2" max="3"/>
-    <col width="12.83203125" customWidth="1" min="4" max="4"/>
-    <col width="7.1640625" customWidth="1" min="5" max="5"/>
-    <col width="31.1640625" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="36.33203125" customWidth="1"/>
+    <col min="2" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="7.1640625" customWidth="1"/>
+    <col min="6" max="6" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Term</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Calendar Year</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Hours</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="17" customHeight="1"/>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A1:F79">
-    <sortState ref="A63:F79">
-      <sortCondition ref="D1:D79"/>
-    </sortState>
-  </autoFilter>
-  <dataValidations count="4">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>Notes!$A$5:$A$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>Notes!$A$10:$A$13</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" operator="between">
+  <dataValidations count="2">
+    <dataValidation type="whole" sqref="D2:D1048576" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>1900</formula1>
       <formula2>2100</formula2>
     </dataValidation>
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThan">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" sqref="E2:E1048576" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000000000000}">
+          <x14:formula1>
+            <xm:f>Notes!$A$5:$A$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000001000000}">
+          <x14:formula1>
+            <xm:f>Notes!$A$10:$A$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>